--- a/Tasks/Task_701_insulin_synthesis/reactions_additions.xlsx
+++ b/Tasks/Task_701_insulin_synthesis/reactions_additions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\MSP_p3_2026_hormone_cytokine_task_creation\Tasks\Task_701_insulin_synthesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\MSP_p3_2026_hormone_cytokine_task_creation\Tasks\Task_701_insulin_synthesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787D77F8-997C-40C6-998B-6C53EEAC715B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1319A853-01FE-4783-AC99-924BF11E6B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rxns" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
   <si>
     <t>action</t>
   </si>
@@ -242,12 +242,6 @@
     <t>o-glycosylated-pro-insulin-2-oxidized-folded-dimerized[s] -&gt; 32-33-pro-insulin[s]</t>
   </si>
   <si>
-    <t>65-55-pro-insulin[s])  -&gt; insulin[s] + C-peptide[s]</t>
-  </si>
-  <si>
-    <t>32-33-pro-insulin[s]   -&gt; insulin[s] + C-peptide[s]</t>
-  </si>
-  <si>
     <t>ENSG00000143742 &amp; ENSG00000140319 &amp; ENSG00000153037 &amp; ENSG00000100883 &amp; ENSG00000167881 &amp; ENSG00000174780</t>
   </si>
   <si>
@@ -335,53 +329,38 @@
     <t>Task 701</t>
   </si>
   <si>
-    <t>Task 702</t>
-  </si>
-  <si>
-    <t>Task 703</t>
-  </si>
-  <si>
-    <t>Task 704</t>
-  </si>
-  <si>
-    <t>Task 705</t>
-  </si>
-  <si>
-    <t>Task 706</t>
-  </si>
-  <si>
-    <t>Task 707</t>
-  </si>
-  <si>
-    <t>Task 708</t>
-  </si>
-  <si>
-    <t>Task 709</t>
-  </si>
-  <si>
-    <t>Task 710</t>
-  </si>
-  <si>
-    <t>Task 711</t>
-  </si>
-  <si>
-    <t>Task 712</t>
-  </si>
-  <si>
-    <t>Task 713</t>
-  </si>
-  <si>
-    <t>Task 714</t>
-  </si>
-  <si>
-    <t>Task 715</t>
+    <t>MAR70115</t>
+  </si>
+  <si>
+    <t>MAR70116</t>
+  </si>
+  <si>
+    <t>des-65-55-pro-insulin[s])  -&gt; insulin[s] + C-peptide[s]</t>
+  </si>
+  <si>
+    <t>des-32-33-pro-insulin[s]   -&gt; insulin[s] + C-peptide[s]</t>
+  </si>
+  <si>
+    <t>ENSG00000109472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65-55-pro-insulin[s] -&gt; des-65-55-pro-insulin[s] </t>
+  </si>
+  <si>
+    <t>32-33-pro-insulin[s] -&gt; des-32-33-pro-insulin[s]</t>
+  </si>
+  <si>
+    <t>Conversion to des-form by CPE</t>
+  </si>
+  <si>
+    <t>CPE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,28 +375,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <u/>
       <sz val="12"/>
       <color theme="1"/>
@@ -447,33 +410,31 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,447 +730,615 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O14" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="J15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="O2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" t="s">
-        <v>98</v>
-      </c>
-      <c r="O3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="H18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="O4" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="L8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" t="s">
-        <v>103</v>
-      </c>
-      <c r="O8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="K18" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="75" x14ac:dyDescent="0.25">
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" t="s">
-        <v>105</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" t="s">
-        <v>63</v>
-      </c>
-      <c r="L11" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.25">
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N12" t="s">
-        <v>107</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L13" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" t="s">
-        <v>108</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="L18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O18" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" t="s">
-        <v>89</v>
-      </c>
-      <c r="L14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N14" t="s">
-        <v>109</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K15" t="s">
-        <v>90</v>
-      </c>
-      <c r="L15" t="s">
-        <v>14</v>
-      </c>
-      <c r="N15" t="s">
-        <v>110</v>
-      </c>
-      <c r="O15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" t="s">
-        <v>14</v>
-      </c>
-      <c r="N16" t="s">
-        <v>111</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L17" s="2"/>
-    </row>
     <row r="75" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L75" s="3"/>
+      <c r="L75" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
